--- a/data/reports/report-2026-08-21.xlsx
+++ b/data/reports/report-2026-08-21.xlsx
@@ -768,23 +768,23 @@
         <v>2.96</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>146245</v>
+        <v>162743</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>49449</v>
+        <v>55890</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>39102</v>
+        <v>42266</v>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="4" t="n">
-        <v>0.113</v>
+        <v>0.16</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -2277,33 +2277,33 @@
         <v>3980</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.3035</v>
+        <v>0.2745</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>1429218</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>433794</v>
+        <v>392323</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>517022</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>478402</v>
+        <v>519873</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.3347</v>
-      </c>
-      <c r="L16" s="17" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="L16" s="18" t="n">
         <v>2.76</v>
       </c>
       <c r="M16" s="5" t="n">
@@ -2313,13 +2313,13 @@
         <v>247736</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>146245</v>
+        <v>162743</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>2.29</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>39102</v>
+        <v>42266</v>
       </c>
       <c r="R16" s="5" t="n">
         <v>35000</v>
@@ -36279,7 +36279,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>売価 3980円 ／ 単価原価 1,182円 ／ 原価率(30日) 30.4% ／ 分岐MER 1.44 ／ 目標MER 2.89</t>
+          <t>売価 3980円 ／ 単価原価 1,069円 ／ 原価率(30日) 27.5% ／ 分岐MER 1.38 ／ 目標MER 2.66</t>
         </is>
       </c>
     </row>
@@ -36349,22 +36349,22 @@
         <v>109052</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>33096</v>
+        <v>29932</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>36854</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>39102</v>
+        <v>42266</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.3586</v>
+        <v>0.3876</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>2.96</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="8">
@@ -36377,22 +36377,22 @@
         <v>222084</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>67374</v>
+        <v>60933</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>105261</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>49449</v>
+        <v>55890</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2227</v>
+        <v>0.2517</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>2.11</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="9">
@@ -36405,22 +36405,22 @@
         <v>566553</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>172572</v>
+        <v>156074</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>247736</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>146245</v>
+        <v>162743</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.2581</v>
+        <v>0.2873</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>2.29</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="10">
@@ -36433,22 +36433,22 @@
         <v>1429218</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>433794</v>
+        <v>392323</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>517022</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>478402</v>
+        <v>519873</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.3347</v>
+        <v>0.3637</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>2.76</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="12">
@@ -38017,22 +38017,22 @@
         <v>3980</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>11820</v>
+        <v>10690</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.297</v>
+        <v>0.2686</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>9546</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>18434</v>
+        <v>19564</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.4632</v>
+        <v>0.4916</v>
       </c>
       <c r="N48" s="18" t="n">
         <v>4.17</v>
@@ -38075,22 +38075,22 @@
         <v>3980</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>5910</v>
+        <v>5345</v>
       </c>
       <c r="J49" s="25" t="n">
-        <v>0.297</v>
+        <v>0.2686</v>
       </c>
       <c r="K49" s="24" t="n">
         <v>10521</v>
       </c>
       <c r="L49" s="24" t="n">
-        <v>3469</v>
+        <v>4034</v>
       </c>
       <c r="M49" s="25" t="n">
-        <v>0.1743</v>
+        <v>0.2027</v>
       </c>
       <c r="N49" s="17" t="n">
         <v>1.89</v>
@@ -38137,22 +38137,22 @@
         <v>3980</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>14184</v>
+        <v>12828</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.302</v>
+        <v>0.2731</v>
       </c>
       <c r="K50" s="5" t="n">
         <v>11079</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>21701</v>
+        <v>23057</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.4621</v>
+        <v>0.491</v>
       </c>
       <c r="N50" s="18" t="n">
         <v>4.24</v>
@@ -38195,22 +38195,22 @@
         <v>3980</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I51" s="24" t="n">
-        <v>16548</v>
+        <v>14966</v>
       </c>
       <c r="J51" s="25" t="n">
-        <v>0.3103</v>
+        <v>0.2806</v>
       </c>
       <c r="K51" s="24" t="n">
         <v>12859</v>
       </c>
       <c r="L51" s="24" t="n">
-        <v>23925</v>
+        <v>25507</v>
       </c>
       <c r="M51" s="25" t="n">
-        <v>0.4486</v>
+        <v>0.4783</v>
       </c>
       <c r="N51" s="18" t="n">
         <v>4.15</v>
@@ -38253,22 +38253,22 @@
         <v>3980</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>18912</v>
+        <v>17104</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.297</v>
+        <v>0.2686</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>17380</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>27388</v>
+        <v>29196</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.4301</v>
+        <v>0.4585</v>
       </c>
       <c r="N52" s="18" t="n">
         <v>3.66</v>
@@ -38315,22 +38315,22 @@
         <v>3980</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I53" s="24" t="n">
-        <v>27186</v>
+        <v>24587</v>
       </c>
       <c r="J53" s="25" t="n">
-        <v>0.3049</v>
+        <v>0.2758</v>
       </c>
       <c r="K53" s="24" t="n">
         <v>21045</v>
       </c>
       <c r="L53" s="24" t="n">
-        <v>40921</v>
+        <v>43520</v>
       </c>
       <c r="M53" s="25" t="n">
-        <v>0.459</v>
+        <v>0.4882</v>
       </c>
       <c r="N53" s="18" t="n">
         <v>4.24</v>
@@ -38373,22 +38373,22 @@
         <v>3980</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>23640</v>
+        <v>21380</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2713</v>
       </c>
       <c r="K54" s="5" t="n">
         <v>19089</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>36075</v>
+        <v>38335</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.4578</v>
+        <v>0.4865</v>
       </c>
       <c r="N54" s="18" t="n">
         <v>4.13</v>
@@ -38435,22 +38435,22 @@
         <v>3980</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>39006</v>
+        <v>35277</v>
       </c>
       <c r="J55" s="25" t="n">
-        <v>0.3044</v>
+        <v>0.2753</v>
       </c>
       <c r="K55" s="24" t="n">
         <v>29199</v>
       </c>
       <c r="L55" s="24" t="n">
-        <v>59951</v>
+        <v>63680</v>
       </c>
       <c r="M55" s="25" t="n">
-        <v>0.4678</v>
+        <v>0.4969</v>
       </c>
       <c r="N55" s="18" t="n">
         <v>4.39</v>
@@ -38497,22 +38497,22 @@
         <v>3980</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>23640</v>
+        <v>21380</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.303</v>
+        <v>0.2741</v>
       </c>
       <c r="K56" s="5" t="n">
         <v>34926</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>19442</v>
+        <v>21702</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.2492</v>
+        <v>0.2782</v>
       </c>
       <c r="N56" s="17" t="n">
         <v>2.23</v>
@@ -38559,22 +38559,22 @@
         <v>3980</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I57" s="24" t="n">
-        <v>24822</v>
+        <v>22449</v>
       </c>
       <c r="J57" s="25" t="n">
-        <v>0.3028</v>
+        <v>0.2738</v>
       </c>
       <c r="K57" s="24" t="n">
         <v>31789</v>
       </c>
       <c r="L57" s="24" t="n">
-        <v>25377</v>
+        <v>27750</v>
       </c>
       <c r="M57" s="25" t="n">
-        <v>0.3095</v>
+        <v>0.3385</v>
       </c>
       <c r="N57" s="17" t="n">
         <v>2.58</v>
@@ -38617,22 +38617,22 @@
         <v>3980</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>26004</v>
+        <v>23518</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.3053</v>
+        <v>0.2761</v>
       </c>
       <c r="K58" s="5" t="n">
         <v>37285</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>21883</v>
+        <v>24369</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.2569</v>
+        <v>0.2861</v>
       </c>
       <c r="N58" s="17" t="n">
         <v>2.28</v>
@@ -38679,22 +38679,22 @@
         <v>3980</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>29550</v>
+        <v>26725</v>
       </c>
       <c r="J59" s="25" t="n">
-        <v>0.3024</v>
+        <v>0.2735</v>
       </c>
       <c r="K59" s="24" t="n">
         <v>32205</v>
       </c>
       <c r="L59" s="24" t="n">
-        <v>35954</v>
+        <v>38779</v>
       </c>
       <c r="M59" s="25" t="n">
-        <v>0.368</v>
+        <v>0.3969</v>
       </c>
       <c r="N59" s="18" t="n">
         <v>3.03</v>
@@ -38737,22 +38737,22 @@
         <v>3980</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>27186</v>
+        <v>24587</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.3022</v>
+        <v>0.2733</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>34215</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>28547</v>
+        <v>31146</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.3174</v>
+        <v>0.3463</v>
       </c>
       <c r="N60" s="17" t="n">
         <v>2.63</v>
@@ -38795,22 +38795,22 @@
         <v>3980</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>23640</v>
+        <v>21380</v>
       </c>
       <c r="J61" s="25" t="n">
-        <v>0.307</v>
+        <v>0.2776</v>
       </c>
       <c r="K61" s="24" t="n">
         <v>31246</v>
       </c>
       <c r="L61" s="24" t="n">
-        <v>22127</v>
+        <v>24387</v>
       </c>
       <c r="M61" s="25" t="n">
-        <v>0.2873</v>
+        <v>0.3167</v>
       </c>
       <c r="N61" s="17" t="n">
         <v>2.46</v>
@@ -38857,22 +38857,22 @@
         <v>3980</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>29550</v>
+        <v>26725</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.3094</v>
+        <v>0.2798</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>45135</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>20835</v>
+        <v>23660</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.2181</v>
+        <v>0.2477</v>
       </c>
       <c r="N62" s="17" t="n">
         <v>2.12</v>
@@ -38915,22 +38915,22 @@
         <v>3980</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>24822</v>
+        <v>22449</v>
       </c>
       <c r="J63" s="25" t="n">
-        <v>0.3028</v>
+        <v>0.2738</v>
       </c>
       <c r="K63" s="24" t="n">
         <v>31879</v>
       </c>
       <c r="L63" s="24" t="n">
-        <v>25287</v>
+        <v>27660</v>
       </c>
       <c r="M63" s="25" t="n">
-        <v>0.3084</v>
+        <v>0.3374</v>
       </c>
       <c r="N63" s="17" t="n">
         <v>2.57</v>
@@ -38973,22 +38973,22 @@
         <v>3980</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>21276</v>
+        <v>19242</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.3072</v>
+        <v>0.2779</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>35549</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>12427</v>
+        <v>14461</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>0.1794</v>
+        <v>0.2088</v>
       </c>
       <c r="N64" s="17" t="n">
         <v>1.95</v>
@@ -39035,22 +39035,22 @@
         <v>3980</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>13002</v>
+        <v>11759</v>
       </c>
       <c r="J65" s="25" t="n">
-        <v>0.297</v>
+        <v>0.2686</v>
       </c>
       <c r="K65" s="24" t="n">
         <v>32858</v>
       </c>
       <c r="L65" s="27" t="n">
-        <v>-2080</v>
+        <v>-837</v>
       </c>
       <c r="M65" s="28" t="n">
-        <v>-0.0475</v>
+        <v>-0.0191</v>
       </c>
       <c r="N65" s="19" t="n">
         <v>1.33</v>
@@ -39089,22 +39089,22 @@
         <v>3980</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>1182</v>
+        <v>1069</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>33096</v>
+        <v>29932</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>0.3035</v>
+        <v>0.2745</v>
       </c>
       <c r="K66" s="5" t="n">
         <v>36854</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>39102</v>
+        <v>42266</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>0.3586</v>
+        <v>0.3876</v>
       </c>
       <c r="N66" s="18" t="n">
         <v>2.96</v>
@@ -63841,37 +63841,37 @@
         <v>567246</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>149308</v>
+        <v>146144</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>304755</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>454063</v>
+        <v>450899</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.8005</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>113183</v>
+        <v>116347</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1995</v>
+        <v>0.2051</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1.86</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>19581</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>93602</v>
+        <v>96766</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.165</v>
+        <v>0.1706</v>
       </c>
     </row>
     <row r="8">
@@ -63884,37 +63884,37 @@
         <v>1576701</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>423056</v>
+        <v>416615</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>892542</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1315598</v>
+        <v>1309157</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.8344</v>
+        <v>0.8303</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>261103</v>
+        <v>267544</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1656</v>
+        <v>0.1697</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>1.77</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>54428</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>206675</v>
+        <v>213116</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1311</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="9">
@@ -63927,37 +63927,37 @@
         <v>4143991</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1120402</v>
+        <v>1103904</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>2279294</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3399696</v>
+        <v>3383198</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.8204</v>
+        <v>0.8164</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>744295</v>
+        <v>760793</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1796</v>
+        <v>0.1836</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>1.82</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>143051</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>601244</v>
+        <v>617742</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1451</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="10">
@@ -63970,22 +63970,22 @@
         <v>29864639</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>8703277</v>
+        <v>8661806</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>13829094</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>22532371</v>
+        <v>22490900</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7531</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>7332268</v>
+        <v>7373739</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2455</v>
+        <v>0.2469</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>2.16</v>
@@ -63997,10 +63997,10 @@
         <v>1030927</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>6301341</v>
+        <v>6342812</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.211</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="11">
@@ -64013,37 +64013,37 @@
         <v>16351926</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4645921</v>
+        <v>4604450</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>8253788</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>12899709</v>
+        <v>12858238</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.7889</v>
+        <v>0.7863</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3452217</v>
+        <v>3493688</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.2111</v>
+        <v>0.2137</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>1.98</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>564468</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>2887749</v>
+        <v>2929220</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1766</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="14">
@@ -64122,20 +64122,20 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>149308</v>
+        <v>146144</v>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="n">
-        <v>141019</v>
+        <v>138872</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>160057</v>
+        <v>157701</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>290109</v>
+        <v>288727</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>-0.0672</v>
+        <v>-0.0733</v>
       </c>
     </row>
     <row r="18">
@@ -64168,20 +64168,20 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>113183</v>
+        <v>116347</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>87034</v>
+        <v>89181</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>106328</v>
+        <v>108685</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>244409</v>
+        <v>245791</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.0645</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -84983,46 +84983,46 @@
         <v>566553</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>172572</v>
+        <v>156074</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>247736</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>146245</v>
+        <v>162743</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2581</v>
+        <v>0.2873</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>2.29</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>109052</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>39102</v>
+        <v>42266</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3586</v>
+        <v>0.3876</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>49449</v>
+        <v>55890</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>478402</v>
+        <v>519873</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>478402</v>
+        <v>519873</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>146</v>
@@ -85037,7 +85037,7 @@
         <v>1795</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>2855</v>
+        <v>2974</v>
       </c>
       <c r="W7" s="5" t="n">
         <v>35000</v>
@@ -87245,22 +87245,22 @@
         <v>2.29</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.113</v>
+        <v>0.16</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>-6935</v>
+        <v>-9790</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>6935</v>
+        <v>9790</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>146245</v>
+        <v>162743</v>
       </c>
     </row>
     <row r="10">
@@ -87895,22 +87895,22 @@
         <v>8643331</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2546622</v>
+        <v>2544927</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>3811440</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2285269</v>
+        <v>2286964</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.2646</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>2.27</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2946</v>
+        <v>0.2944</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0.441</v>
@@ -87922,7 +87922,7 @@
         <v>2.37</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>790219</v>
+        <v>791914</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>2.49</v>
@@ -87938,22 +87938,22 @@
         <v>6176279</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1778993</v>
+        <v>1763399</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>3184330</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1212956</v>
+        <v>1228550</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.1964</v>
+        <v>0.1989</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>1.94</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.288</v>
+        <v>0.2855</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.5155999999999999</v>
@@ -87965,7 +87965,7 @@
         <v>1.78</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>916762</v>
+        <v>932356</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>2.5</v>
@@ -88869,22 +88869,22 @@
         <v>1492118</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>441538</v>
+        <v>440408</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>574619</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>475961</v>
+        <v>477091</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.319</v>
+        <v>0.3197</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>361276</v>
+        <v>361652</v>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
     </row>
@@ -88903,22 +88903,22 @@
         <v>1013035</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>289608</v>
+        <v>289043</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>491866</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>231561</v>
+        <v>232126</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.2286</v>
+        <v>0.2291</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>2.06</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>353773</v>
+        <v>354338</v>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
     </row>
@@ -88937,22 +88937,22 @@
         <v>1022649</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>296775</v>
+        <v>295419</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>548534</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>177340</v>
+        <v>178696</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1734</v>
+        <v>0.1747</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>1.86</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>294954</v>
+        <v>295971</v>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
     </row>
@@ -88971,22 +88971,22 @@
         <v>837101</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>248436</v>
+        <v>246854</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>476255</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>112410</v>
+        <v>113992</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.1343</v>
+        <v>0.1362</v>
       </c>
       <c r="H28" s="9" t="n">
         <v>1.76</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>173770</v>
+        <v>174938</v>
       </c>
       <c r="J28" s="4" t="inlineStr"/>
     </row>
@@ -89005,22 +89005,22 @@
         <v>798238</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>220873</v>
+        <v>219065</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>441601</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>135764</v>
+        <v>137572</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1701</v>
+        <v>0.1723</v>
       </c>
       <c r="H29" s="9" t="n">
         <v>1.81</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>141838</v>
+        <v>143420</v>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
     </row>
@@ -89039,22 +89039,22 @@
         <v>880324</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>246246</v>
+        <v>243647</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>396343</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>237735</v>
+        <v>240334</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2701</v>
+        <v>0.273</v>
       </c>
       <c r="H30" s="9" t="n">
         <v>2.22</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>161970</v>
+        <v>163966</v>
       </c>
       <c r="J30" s="4" t="inlineStr"/>
     </row>
@@ -89073,22 +89073,22 @@
         <v>950121</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>281915</v>
+        <v>279655</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>453944</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>214262</v>
+        <v>216522</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.2255</v>
+        <v>0.2279</v>
       </c>
       <c r="H31" s="9" t="n">
         <v>2.09</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>195920</v>
+        <v>198142</v>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
     </row>
@@ -89107,22 +89107,22 @@
         <v>963228</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>280667</v>
+        <v>276938</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>472090</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>210471</v>
+        <v>214200</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.2185</v>
+        <v>0.2224</v>
       </c>
       <c r="H32" s="9" t="n">
         <v>2.04</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>220822</v>
+        <v>223685</v>
       </c>
       <c r="J32" s="4" t="inlineStr"/>
     </row>
@@ -89141,22 +89141,22 @@
         <v>724618</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>204081</v>
+        <v>201821</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>395563</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>124974</v>
+        <v>127234</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.1725</v>
+        <v>0.1756</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>1.83</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>183236</v>
+        <v>185985</v>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
     </row>
@@ -89175,22 +89175,22 @@
         <v>896607</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>249187</v>
+        <v>246814</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>438612</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>208808</v>
+        <v>211181</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.2329</v>
+        <v>0.2355</v>
       </c>
       <c r="H34" s="9" t="n">
         <v>2.04</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>181418</v>
+        <v>184205</v>
       </c>
       <c r="J34" s="4" t="inlineStr"/>
     </row>
@@ -89209,22 +89209,22 @@
         <v>674797</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>195514</v>
+        <v>193028</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>361905</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>117378</v>
+        <v>119864</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.1739</v>
+        <v>0.1776</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>1.86</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>150387</v>
+        <v>152760</v>
       </c>
       <c r="J35" s="4" t="inlineStr"/>
     </row>
@@ -89243,22 +89243,22 @@
         <v>654823</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>183167</v>
+        <v>180342</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>362846</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>108810</v>
+        <v>111635</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.1662</v>
+        <v>0.1705</v>
       </c>
       <c r="H36" s="9" t="n">
         <v>1.8</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>144999</v>
+        <v>147560</v>
       </c>
       <c r="J36" s="4" t="inlineStr"/>
     </row>
@@ -89277,22 +89277,22 @@
         <v>590204</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>155406</v>
+        <v>152807</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>363324</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>71474</v>
+        <v>74073</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.1211</v>
+        <v>0.1255</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>1.62</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>99221</v>
+        <v>101857</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -89315,22 +89315,22 @@
         <v>769897</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>209693</v>
+        <v>207433</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>364579</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>195625</v>
+        <v>197885</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.2541</v>
+        <v>0.257</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>2.11</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>125303</v>
+        <v>127864</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -89353,22 +89353,22 @@
         <v>714403</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>199333</v>
+        <v>196508</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>382657</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>132413</v>
+        <v>135238</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.1853</v>
+        <v>0.1893</v>
       </c>
       <c r="H39" s="9" t="n">
         <v>1.87</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>133171</v>
+        <v>135732</v>
       </c>
       <c r="J39" s="4" t="inlineStr"/>
     </row>
@@ -89387,22 +89387,22 @@
         <v>492786</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>134213</v>
+        <v>131840</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>276192</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>82381</v>
+        <v>84754</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.1672</v>
+        <v>0.172</v>
       </c>
       <c r="H40" s="9" t="n">
         <v>1.78</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>136806</v>
+        <v>139292</v>
       </c>
       <c r="J40" s="4" t="inlineStr"/>
     </row>
@@ -89421,22 +89421,22 @@
         <v>469714</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>128891</v>
+        <v>126857</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>303447</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>37376</v>
+        <v>39410</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.0796</v>
+        <v>0.0839</v>
       </c>
       <c r="H41" s="9" t="n">
         <v>1.55</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>84057</v>
+        <v>86468</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -89459,22 +89459,22 @@
         <v>539741</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>144940</v>
+        <v>143697</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>284340</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>110461</v>
+        <v>111704</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.2047</v>
+        <v>0.207</v>
       </c>
       <c r="H42" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>76740</v>
+        <v>78623</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -89497,22 +89497,22 @@
         <v>567246</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>149492</v>
+        <v>146328</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>304755</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>112999</v>
+        <v>116163</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.1992</v>
+        <v>0.2048</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>1.86</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>86945</v>
+        <v>89092</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
